--- a/小野町_引継ぎ_整理済/20_総合事業ワークシート/小野町_総合事業ワークシート_小野町のデータ_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/20_総合事業ワークシート/小野町_総合事業ワークシート_小野町のデータ_20260928.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>小野町は訪問型サービスB・通所型サービスB（住民主体によるサービス）を実施していることが分かりました。国の調査に「実施の有無＝有」と回答されています。これまで実施の有無が確認できていなかったものが判明しました（第2章3）</t>
+          <t>小野町には訪問型サービスB・通所型サービスB（住民主体によるサービス）が置かれています。国の調査に「実施の有無＝有」（令和元年度〜令和3年度）と回答され、市町村内の事業所（団体）数は平成29年度から令和4年度まで各1で一貫しています。ただし令和4年度・令和5年度の実施の有無は無回答で、令和5年度の利用者数は訪問型B 24人に対し通所型Bは0人です。現在も実施しているかは町にご確認ください（第2章3）</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ただし、調査への回答は年度ごとにばらつきが大きく、そのままでは時系列の比較に使えません。従前相当サービスの利用者数がほとんど空欄で、実人数と延べ人数が同じ年があり、サービスBの人数が408人→24人→150人→24人と激しく振れています（第2章3）</t>
+          <t>調査への回答には、そのままでは使えない不整合が3つあります。①従前相当サービスの利用者数がほとんど空欄で、実人数と延べ人数が同じ年があり、サービスBの人数が408人→24人→150人→24人と激しく振れています。②従前相当サービスの実施の有無が令和3年度は「無」ですが、令和5年度の利用者数は訪問型23人・通所型54人あり、国保連月報にも毎月の実績があります。③介護予防ケアマネジメントAの実施の有無が令和4年度だけ「無」ですが、同年度の実施件数は52件です。②③は回答そのものの誤りとみられます（第2章3）</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>人材の視点では、2030年に供給が需要に追いつかない見通しになります。生産年齢人口は2020年の4,677人から2050年の2,399人へ半減する一方、認定者数は横ばいです。第10期（令和9〜11年度）はまだ持ちますが、その直後から効いてきます（第3章）</t>
+          <t>人材の視点では、2030年に供給が需要に追いつかなくなる見通しです。生産年齢人口は2020年の4,677人から2050年の2,399人へ半減する一方、認定者数は横ばいです。ただしこれは、介護人材が生産年齢人口に比例して減ること、2020年時点では過不足がないことを置いた、ワークシートの考え方による試算です。町の介護人材の実数を数えたものではありません（第3章）</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>ワークシートの将来推計人口が、見える化システムの第1号被保険者数と完全に一致することを確かめました。2030年3,406人・2035年3,206人・2040年2,993人・2045年2,818人・2050年2,565人。どちらも社人研の令和5年推計によるもので、算定の土台は揺らぎません（第2章1）</t>
+          <t>ワークシートの65歳以上人口が、見える化システムの人口指標（A2 高齢者数）と1人まで一致することを確かめました。2030年3,406人・2035年3,206人・2040年2,993人・2045年2,818人・2050年2,565人。どちらも社人研の令和5年推計によるもので、出所が同じことの裏づけです。なお、保険料算定に用いている第1号被保険者数は町のコーホート変化率法による別系列（令和9年度3,438人）であり、この一致は保険料算定そのものを裏づけるものではありません（第2章1）</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1737,12 +1737,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>通所型　従前相当</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>有</t>
+          <t>訪問型サービスC（短期集中）</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>無</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -1767,7 +1767,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>通所型サービスA</t>
+          <t>訪問型サービスD（移動支援）</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -1797,7 +1797,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>通所型サービスB（住民主体）</t>
+          <t>通所型　従前相当</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
@@ -1805,14 +1805,14 @@
           <t>有</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>有</t>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>無</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -1827,12 +1827,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>介護予防ケアマネジメントA</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>有</t>
+          <t>通所型サービスA</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>無</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -1840,14 +1840,14 @@
           <t>―</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>有</t>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="F22" s="2" t="n"/>
@@ -1857,27 +1857,27 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>介護予防ケアマネジメントB</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>無</t>
+          <t>通所型サービスB（住民主体）</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="F23" s="2" t="n"/>
@@ -1887,12 +1887,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>介護予防ケアマネジメントC</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>―</t>
+          <t>通所型サービスC（短期集中）</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>無</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -1905,14 +1905,104 @@
           <t>無</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>無</t>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>介護予防ケアマネジメントA</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>介護予防ケアマネジメントB</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>介護予防ケアマネジメントC</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2061,7 +2151,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>実施していることが分かりました。第10期の重点施策の土台になるため、中身を教えてください</t>
+          <t>事業所（団体）が各1あることまでは分かりました。令和4年度以降の実施の有無が無回答で、令和5年度の通所型Bは0人です。現在も実施しているかを含めて、中身を教えてください</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
